--- a/docs/Mapping_casi_uso/matrimoni/Matr_998_3.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_998_3.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="143">
   <si>
     <t>Sezione</t>
   </si>
@@ -110,24 +110,186 @@
     <t>idANPR</t>
   </si>
   <si>
-    <t>Codice Fiscale</t>
-  </si>
-  <si>
-    <t>codiceFiscale</t>
-  </si>
-  <si>
     <t>Sesso</t>
   </si>
   <si>
     <t>sesso</t>
   </si>
   <si>
+    <t>Formato Data Nascita</t>
+  </si>
+  <si>
+    <t>idFormatodata</t>
+  </si>
+  <si>
+    <t>Formato Data Nascita - Descrizione</t>
+  </si>
+  <si>
+    <t>formatodata</t>
+  </si>
+  <si>
     <t>Data nascita</t>
   </si>
   <si>
     <t>dataNascita</t>
   </si>
   <si>
+    <t>Stato di nascita</t>
+  </si>
+  <si>
+    <t>idStatoNascita</t>
+  </si>
+  <si>
+    <t>Stato di nascita - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeStatoNascita</t>
+  </si>
+  <si>
+    <t>Provincia di nascita</t>
+  </si>
+  <si>
+    <t>idProvinciaNascita</t>
+  </si>
+  <si>
+    <t>Provincia di nascita - Descrizione</t>
+  </si>
+  <si>
+    <t>siglaProvinciaNascita</t>
+  </si>
+  <si>
+    <t>Comune di nascita</t>
+  </si>
+  <si>
+    <t>idComuneNascita</t>
+  </si>
+  <si>
+    <t>Comune di nascita - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeComuneNascita</t>
+  </si>
+  <si>
+    <t>Località estera</t>
+  </si>
+  <si>
+    <t>localitaEsteraNascita</t>
+  </si>
+  <si>
+    <t>Nazionalità</t>
+  </si>
+  <si>
+    <t>idNazionalita</t>
+  </si>
+  <si>
+    <t>Nazionalità - Descrizione</t>
+  </si>
+  <si>
+    <t>nazionalita</t>
+  </si>
+  <si>
+    <t>Comprensione</t>
+  </si>
+  <si>
+    <t>tipoImpedimento</t>
+  </si>
+  <si>
+    <t>Residenza non nota</t>
+  </si>
+  <si>
+    <t>flagIrreperibile</t>
+  </si>
+  <si>
+    <t>Stato di residenza</t>
+  </si>
+  <si>
+    <t>idStatoResidenza</t>
+  </si>
+  <si>
+    <t>Stato di residenza - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeStatoResidenza</t>
+  </si>
+  <si>
+    <t>Provincia di residenza</t>
+  </si>
+  <si>
+    <t>idProvinciaResidenza</t>
+  </si>
+  <si>
+    <t>Provincia di residenza - Descrizione</t>
+  </si>
+  <si>
+    <t>siglaProvinciaResidenza</t>
+  </si>
+  <si>
+    <t>Comune di residenza</t>
+  </si>
+  <si>
+    <t>idComuneResidenza</t>
+  </si>
+  <si>
+    <t>Comune di residenza - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeComuneResidenza</t>
+  </si>
+  <si>
+    <t>Indirizzo di residenza</t>
+  </si>
+  <si>
+    <t>indirizzoResidenza</t>
+  </si>
+  <si>
+    <t>flag dichiarante</t>
+  </si>
+  <si>
+    <t>flagDichiarante</t>
+  </si>
+  <si>
+    <t>flag comparente</t>
+  </si>
+  <si>
+    <t>flagComparente</t>
+  </si>
+  <si>
+    <t>flag firmatario</t>
+  </si>
+  <si>
+    <t>flagFirmatario</t>
+  </si>
+  <si>
+    <t>Età(anni)</t>
+  </si>
+  <si>
+    <t>anni</t>
+  </si>
+  <si>
+    <t>Provincia AIRE</t>
+  </si>
+  <si>
+    <t>idProvinciaAIRE</t>
+  </si>
+  <si>
+    <t>Provincia AIRE - Descrizione</t>
+  </si>
+  <si>
+    <t>siglaProvinciaAIRE</t>
+  </si>
+  <si>
+    <t>Comune AIRE</t>
+  </si>
+  <si>
+    <t>idComuneAIRE</t>
+  </si>
+  <si>
+    <t>Comune AIRE - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeComuneAIRE</t>
+  </si>
+  <si>
     <t>Data morte</t>
   </si>
   <si>
@@ -137,102 +299,6 @@
     <t>dataMorte</t>
   </si>
   <si>
-    <t>Stato Nascita</t>
-  </si>
-  <si>
-    <t>idStatoNascita</t>
-  </si>
-  <si>
-    <t>Stato Nascita - Descrizione</t>
-  </si>
-  <si>
-    <t>nomeStatoNascita</t>
-  </si>
-  <si>
-    <t>Provincia Nascita</t>
-  </si>
-  <si>
-    <t>idProvinciaNascita</t>
-  </si>
-  <si>
-    <t>Provincia Nascita - Descrizione</t>
-  </si>
-  <si>
-    <t>siglaProvinciaNascita</t>
-  </si>
-  <si>
-    <t>Comune Nascita</t>
-  </si>
-  <si>
-    <t>idComuneNascita</t>
-  </si>
-  <si>
-    <t>Comune Nascita - Descrizione</t>
-  </si>
-  <si>
-    <t>nomeComuneNascita</t>
-  </si>
-  <si>
-    <t>Località estera</t>
-  </si>
-  <si>
-    <t>localitaEsteraNascita</t>
-  </si>
-  <si>
-    <t>Nazionalità</t>
-  </si>
-  <si>
-    <t>idNazionalita</t>
-  </si>
-  <si>
-    <t>Nazionalità   - Descrizione</t>
-  </si>
-  <si>
-    <t>nazionalita</t>
-  </si>
-  <si>
-    <t>Stato Residenza</t>
-  </si>
-  <si>
-    <t>idStatoResidenza</t>
-  </si>
-  <si>
-    <t>Stato Residenza - Descrizione</t>
-  </si>
-  <si>
-    <t>nomeStatoResidenza</t>
-  </si>
-  <si>
-    <t>Provincia Residenza</t>
-  </si>
-  <si>
-    <t>idProvinciaResidenza</t>
-  </si>
-  <si>
-    <t>Provincia Residenza - Descrizione</t>
-  </si>
-  <si>
-    <t>siglaProvinciaResidenza</t>
-  </si>
-  <si>
-    <t>Comune Residenza</t>
-  </si>
-  <si>
-    <t>idComuneResidenza</t>
-  </si>
-  <si>
-    <t>Comune Residenza - Descrizione</t>
-  </si>
-  <si>
-    <t>nomeComuneResidenza</t>
-  </si>
-  <si>
-    <t>Indirizzo Residenza</t>
-  </si>
-  <si>
-    <t>indirizzoResidenza</t>
-  </si>
-  <si>
     <t>Atto di riferimento</t>
   </si>
   <si>
@@ -315,90 +381,6 @@
   </si>
   <si>
     <t>evento.datiAnnotazioneModificativa.soggettoCollegato</t>
-  </si>
-  <si>
-    <t>Formato Data Nascita</t>
-  </si>
-  <si>
-    <t>idFormatodata</t>
-  </si>
-  <si>
-    <t>Formato Data Nascita - Descrizione</t>
-  </si>
-  <si>
-    <t>formatodata</t>
-  </si>
-  <si>
-    <t>Stato di nascita</t>
-  </si>
-  <si>
-    <t>Stato di nascita - Descrizione</t>
-  </si>
-  <si>
-    <t>Provincia di nascita</t>
-  </si>
-  <si>
-    <t>Provincia di nascita - Descrizione</t>
-  </si>
-  <si>
-    <t>Comune di nascita</t>
-  </si>
-  <si>
-    <t>Comune di nascita - Descrizione</t>
-  </si>
-  <si>
-    <t>Nazionalità - Descrizione</t>
-  </si>
-  <si>
-    <t>Comprensione</t>
-  </si>
-  <si>
-    <t>tipoImpedimento</t>
-  </si>
-  <si>
-    <t>Residenza non nota</t>
-  </si>
-  <si>
-    <t>flagIrreperibile</t>
-  </si>
-  <si>
-    <t>Stato di residenza</t>
-  </si>
-  <si>
-    <t>Stato di residenza - Descrizione</t>
-  </si>
-  <si>
-    <t>Provincia di residenza</t>
-  </si>
-  <si>
-    <t>Provincia di residenza - Descrizione</t>
-  </si>
-  <si>
-    <t>Comune di residenza</t>
-  </si>
-  <si>
-    <t>Comune di residenza - Descrizione</t>
-  </si>
-  <si>
-    <t>Indirizzo di residenza</t>
-  </si>
-  <si>
-    <t>flag dichiarante</t>
-  </si>
-  <si>
-    <t>flagDichiarante</t>
-  </si>
-  <si>
-    <t>flag comparente</t>
-  </si>
-  <si>
-    <t>flagComparente</t>
-  </si>
-  <si>
-    <t>flag firmatario</t>
-  </si>
-  <si>
-    <t>flagFirmatario</t>
   </si>
   <si>
     <t>Dati generali</t>
@@ -517,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -767,7 +749,7 @@
         <v>32</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>26</v>
@@ -790,7 +772,7 @@
         <v>34</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>26</v>
@@ -813,7 +795,7 @@
         <v>36</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>26</v>
@@ -839,10 +821,10 @@
         <v>25</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
@@ -856,16 +838,16 @@
         <v>23</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>10</v>
@@ -879,16 +861,16 @@
         <v>23</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>10</v>
@@ -902,16 +884,16 @@
         <v>23</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>10</v>
@@ -925,16 +907,16 @@
         <v>23</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>10</v>
@@ -948,16 +930,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>10</v>
@@ -971,16 +953,16 @@
         <v>23</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>10</v>
@@ -994,16 +976,16 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>10</v>
@@ -1017,16 +999,16 @@
         <v>23</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>10</v>
@@ -1040,16 +1022,16 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>10</v>
@@ -1063,16 +1045,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>10</v>
@@ -1086,16 +1068,16 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>10</v>
@@ -1109,16 +1091,16 @@
         <v>23</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>10</v>
@@ -1132,16 +1114,16 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>10</v>
@@ -1155,16 +1137,16 @@
         <v>23</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>10</v>
@@ -1178,16 +1160,16 @@
         <v>23</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>10</v>
@@ -1201,16 +1183,16 @@
         <v>23</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>10</v>
@@ -1221,19 +1203,19 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>10</v>
@@ -1244,19 +1226,19 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>10</v>
@@ -1267,19 +1249,19 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>10</v>
@@ -1290,19 +1272,19 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>10</v>
@@ -1313,19 +1295,19 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>10</v>
@@ -1336,19 +1318,19 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>10</v>
@@ -1359,19 +1341,19 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>10</v>
@@ -1382,19 +1364,19 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>10</v>
@@ -1405,19 +1387,19 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>10</v>
@@ -1428,19 +1410,19 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>10</v>
@@ -1451,16 +1433,16 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>94</v>
@@ -1474,19 +1456,19 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>10</v>
@@ -1497,19 +1479,19 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="E43" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>10</v>
@@ -1520,19 +1502,19 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>10</v>
@@ -1543,19 +1525,19 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>29</v>
+        <v>104</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>10</v>
@@ -1566,19 +1548,19 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>10</v>
@@ -1589,19 +1571,19 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>10</v>
@@ -1612,19 +1594,19 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>10</v>
@@ -1635,19 +1617,19 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>10</v>
@@ -1658,19 +1640,19 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>10</v>
@@ -1681,19 +1663,19 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>10</v>
@@ -1704,19 +1686,19 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>10</v>
@@ -1727,19 +1709,19 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>10</v>
@@ -1750,19 +1732,19 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>10</v>
@@ -1773,19 +1755,19 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>10</v>
@@ -1796,19 +1778,19 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>10</v>
@@ -1819,19 +1801,19 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>10</v>
@@ -1842,19 +1824,19 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>10</v>
@@ -1865,19 +1847,19 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>10</v>
@@ -1888,19 +1870,19 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>10</v>
@@ -1911,19 +1893,19 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>10</v>
@@ -1934,19 +1916,19 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>10</v>
@@ -1957,19 +1939,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
@@ -1980,19 +1962,19 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>10</v>
@@ -2003,19 +1985,19 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>10</v>
@@ -2026,19 +2008,19 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>10</v>
@@ -2049,19 +2031,19 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>10</v>
@@ -2072,19 +2054,19 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>10</v>
@@ -2095,19 +2077,19 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>10</v>
@@ -2118,19 +2100,19 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>126</v>
+        <v>57</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>10</v>
@@ -2141,19 +2123,19 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>127</v>
+        <v>58</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>128</v>
+        <v>59</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>10</v>
@@ -2164,203 +2146,203 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>132</v>
+        <v>61</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>133</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>135</v>
+        <v>63</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>133</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>137</v>
+        <v>65</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>133</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>139</v>
+        <v>67</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>133</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>140</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>140</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>136</v>
+        <v>72</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>137</v>
+        <v>73</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>141</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>138</v>
+        <v>74</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>141</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>14</v>
+        <v>122</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
@@ -2371,19 +2353,19 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>14</v>
+        <v>122</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>10</v>
@@ -2394,24 +2376,277 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D82" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E85" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E82" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G82" s="2" t="s">
+      <c r="F85" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G93" s="2" t="s">
         <v>16</v>
       </c>
     </row>
